--- a/data/total.xlsx
+++ b/data/total.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M346"/>
+  <dimension ref="A1:L346"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -402,20 +402,15 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>geometry</t>
+          <t>url</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>url</t>
+          <t>dedicated_to</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>dedicated_to</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>website</t>
         </is>
@@ -9452,12 +9447,12 @@
       <c r="E228">
         <v>10280</v>
       </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/911-memorial-st-josephs-chapel</t>
+        </is>
+      </c>
       <c r="K228" t="inlineStr">
-        <is>
-          <t>https://voicescenter.org/living-memorial/memorials/911-memorial-st-josephs-chapel</t>
-        </is>
-      </c>
-      <c r="L228" t="inlineStr">
         <is>
           <t>Those who died and those who took part in the rescue efforts of September 11, 2001.</t>
         </is>
@@ -9482,17 +9477,17 @@
       <c r="E229">
         <v>11385</v>
       </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/911-memorial-garden-and-stone</t>
+        </is>
+      </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>https://voicescenter.org/living-memorial/memorials/911-memorial-garden-and-stone</t>
+          <t>42 neighbors and friends from the Glendale, Middle Village, Ridgewood and Woodhaven communites killed on 9/11.</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
-        <is>
-          <t>42 neighbors and friends from the Glendale, Middle Village, Ridgewood and Woodhaven communites killed on 9/11.</t>
-        </is>
-      </c>
-      <c r="M229" t="inlineStr">
         <is>
           <t>https://www.911memorialgarden.org/</t>
         </is>
@@ -9512,12 +9507,12 @@
       <c r="E230">
         <v>10007</v>
       </c>
-      <c r="K230" t="inlineStr">
+      <c r="J230" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/1993-wtc-bombing-memorial</t>
         </is>
       </c>
-      <c r="M230" t="inlineStr">
+      <c r="L230" t="inlineStr">
         <is>
           <t>https://www.911memorial.org/</t>
         </is>
@@ -9537,12 +9532,12 @@
       <c r="E231">
         <v>10003</v>
       </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/911-memorial-wall-fountain</t>
+        </is>
+      </c>
       <c r="K231" t="inlineStr">
-        <is>
-          <t>https://voicescenter.org/living-memorial/memorials/911-memorial-wall-fountain</t>
-        </is>
-      </c>
-      <c r="L231" t="inlineStr">
         <is>
           <t>Six Graduates of NYU School of Law</t>
         </is>
@@ -9562,12 +9557,12 @@
       <c r="E232">
         <v>10009</v>
       </c>
-      <c r="K232" t="inlineStr">
+      <c r="J232" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/14th-street-911-memorial</t>
         </is>
       </c>
-      <c r="M232" t="inlineStr">
+      <c r="L232" t="inlineStr">
         <is>
           <t>https://groundzeromuseumworkshop.org/</t>
         </is>
@@ -9593,7 +9588,7 @@
       <c r="E233">
         <v>10304</v>
       </c>
-      <c r="K233" t="inlineStr">
+      <c r="J233" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/alexander-robbins-steinman-memorial-field</t>
         </is>
@@ -9620,12 +9615,12 @@
       <c r="E234">
         <v>11224</v>
       </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/amalgamated-warbasse-house-brooklyn-new-york</t>
+        </is>
+      </c>
       <c r="K234" t="inlineStr">
-        <is>
-          <t>https://voicescenter.org/living-memorial/memorials/amalgamated-warbasse-house-brooklyn-new-york</t>
-        </is>
-      </c>
-      <c r="L234" t="inlineStr">
         <is>
           <t>Victims and recovery workers by the Amalgamated Warbasse Houses Inc. and Caring Cooperators</t>
         </is>
@@ -9652,12 +9647,12 @@
       <c r="E235">
         <v>10305</v>
       </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/angels-circle-wtc-memorial</t>
+        </is>
+      </c>
       <c r="K235" t="inlineStr">
-        <is>
-          <t>https://voicescenter.org/living-memorial/memorials/angels-circle-wtc-memorial</t>
-        </is>
-      </c>
-      <c r="L235" t="inlineStr">
         <is>
           <t>The nearly 170 Staten Islanders who were killed during the terrorist attacks on the World Trade Center</t>
         </is>
@@ -9682,12 +9677,12 @@
       <c r="E236">
         <v>11365</v>
       </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/bench-st-francis-prep-high-school</t>
+        </is>
+      </c>
       <c r="K236" t="inlineStr">
-        <is>
-          <t>https://voicescenter.org/living-memorial/memorials/bench-st-francis-prep-high-school</t>
-        </is>
-      </c>
-      <c r="L236" t="inlineStr">
         <is>
           <t>Michael A. Marti</t>
         </is>
@@ -9712,17 +9707,17 @@
       <c r="E237">
         <v>10023</v>
       </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/blake-wallens-memorial-bench</t>
+        </is>
+      </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>https://voicescenter.org/living-memorial/memorials/blake-wallens-memorial-bench</t>
+          <t>Blake Wallens</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
-        <is>
-          <t>Blake Wallens</t>
-        </is>
-      </c>
-      <c r="M237" t="inlineStr">
         <is>
           <t>www.riversideparkfund.org</t>
         </is>
@@ -9747,17 +9742,17 @@
       <c r="E238">
         <v>11697</v>
       </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/breezy-point-911-memorial</t>
+        </is>
+      </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>https://voicescenter.org/living-memorial/memorials/breezy-point-911-memorial</t>
+          <t>Residents of Breezy Point (29)</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
-        <is>
-          <t>Residents of Breezy Point (29)</t>
-        </is>
-      </c>
-      <c r="M238" t="inlineStr">
         <is>
           <t>http://www.unyquefiretrucks.com/9_11_-_Point_Breeze.html</t>
         </is>
@@ -9777,12 +9772,12 @@
       <c r="E239">
         <v>10314</v>
       </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/brian-e-bilcher-way</t>
+        </is>
+      </c>
       <c r="K239" t="inlineStr">
-        <is>
-          <t>https://voicescenter.org/living-memorial/memorials/brian-e-bilcher-way</t>
-        </is>
-      </c>
-      <c r="L239" t="inlineStr">
         <is>
           <t>Brian Bilcher</t>
         </is>
@@ -9810,12 +9805,12 @@
       <c r="E240">
         <v>11201</v>
       </c>
-      <c r="K240" t="inlineStr">
+      <c r="J240" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/brooklyn-bridge-park-coalition-memorial-garden</t>
         </is>
       </c>
-      <c r="M240" t="inlineStr">
+      <c r="L240" t="inlineStr">
         <is>
           <t>www.brooklynbridgepark.org</t>
         </is>
@@ -9840,17 +9835,17 @@
       <c r="E241">
         <v>11209</v>
       </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/brooklyn-remembers-memorial</t>
+        </is>
+      </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>https://voicescenter.org/living-memorial/memorials/brooklyn-remembers-memorial</t>
+          <t>Brooklyn victims of the World Trade Center attacks</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
-        <is>
-          <t>Brooklyn victims of the World Trade Center attacks</t>
-        </is>
-      </c>
-      <c r="M241" t="inlineStr">
         <is>
           <t>http://www.brooklynartscouncil.org/files/downloads/BrooklynRemembers05_program-1.pdf</t>
         </is>
@@ -9879,12 +9874,12 @@
       <c r="E242">
         <v>11224</v>
       </c>
-      <c r="K242" t="inlineStr">
+      <c r="J242" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/brooklyn-wall-rememberance</t>
         </is>
       </c>
-      <c r="M242" t="inlineStr">
+      <c r="L242" t="inlineStr">
         <is>
           <t>http://www.brooklynwall.org/</t>
         </is>
@@ -9904,12 +9899,12 @@
       <c r="E243">
         <v>10003</v>
       </c>
-      <c r="K243" t="inlineStr">
+      <c r="J243" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/brotherhood-synagogue</t>
         </is>
       </c>
-      <c r="M243" t="inlineStr">
+      <c r="L243" t="inlineStr">
         <is>
           <t>http://brotherhoodsynagogue.org/</t>
         </is>
@@ -9929,7 +9924,7 @@
       <c r="E244">
         <v>10024</v>
       </c>
-      <c r="K244" t="inlineStr">
+      <c r="J244" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/central-park-tree-trust-memorial</t>
         </is>
@@ -9954,7 +9949,7 @@
       <c r="E245">
         <v>11368</v>
       </c>
-      <c r="K245" t="inlineStr">
+      <c r="J245" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/citi-field-memorial-plaque</t>
         </is>
@@ -9981,17 +9976,17 @@
       <c r="E246">
         <v>10036</v>
       </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/clinton-community-garden-hells-kitchen-fire-heroes-benefit-concert</t>
+        </is>
+      </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>https://voicescenter.org/living-memorial/memorials/clinton-community-garden-hells-kitchen-fire-heroes-benefit-concert</t>
+          <t>The firefighters and their families from the Hell's Kitchen Fire Houses</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
-        <is>
-          <t>The firefighters and their families from the Hell's Kitchen Fire Houses</t>
-        </is>
-      </c>
-      <c r="M246" t="inlineStr">
         <is>
           <t>www.clintoncommunitygarden.org</t>
         </is>
@@ -10011,12 +10006,12 @@
       <c r="E247">
         <v>11211</v>
       </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/conseleya-911-memorial</t>
+        </is>
+      </c>
       <c r="K247" t="inlineStr">
-        <is>
-          <t>https://voicescenter.org/living-memorial/memorials/conseleya-911-memorial</t>
-        </is>
-      </c>
-      <c r="L247" t="inlineStr">
         <is>
           <t>Victims of September 11</t>
         </is>
@@ -10036,7 +10031,7 @@
       <c r="E248">
         <v>10312</v>
       </c>
-      <c r="K248" t="inlineStr">
+      <c r="J248" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/crescent-beach-park-flagpolememorial-911-victims</t>
         </is>
@@ -10056,12 +10051,12 @@
       <c r="E249">
         <v>10019</v>
       </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/david-d-alger-memorial</t>
+        </is>
+      </c>
       <c r="K249" t="inlineStr">
-        <is>
-          <t>https://voicescenter.org/living-memorial/memorials/david-d-alger-memorial</t>
-        </is>
-      </c>
-      <c r="L249" t="inlineStr">
         <is>
           <t>David D. Alger and those who perished on 9/11/01</t>
         </is>
@@ -10086,12 +10081,12 @@
       <c r="E250">
         <v>7302</v>
       </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/diane-gail-barry-memorial</t>
+        </is>
+      </c>
       <c r="K250" t="inlineStr">
-        <is>
-          <t>https://voicescenter.org/living-memorial/memorials/diane-gail-barry-memorial</t>
-        </is>
-      </c>
-      <c r="L250" t="inlineStr">
         <is>
           <t>Diane Gail Barry</t>
         </is>
@@ -10111,7 +10106,7 @@
       <c r="E251">
         <v>10012</v>
       </c>
-      <c r="K251" t="inlineStr">
+      <c r="J251" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/douglas-b-and-joseph-h-gardner-commons</t>
         </is>
@@ -10146,7 +10141,7 @@
       <c r="E252">
         <v>10463</v>
       </c>
-      <c r="K252" t="inlineStr">
+      <c r="J252" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/endor-community-garden</t>
         </is>
@@ -10171,7 +10166,7 @@
       <c r="E253">
         <v>11233</v>
       </c>
-      <c r="K253" t="inlineStr">
+      <c r="J253" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/engine-227-truck</t>
         </is>
@@ -10196,7 +10191,7 @@
       <c r="E254">
         <v>10013</v>
       </c>
-      <c r="K254" t="inlineStr">
+      <c r="J254" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/engine-55-battalion-2</t>
         </is>
@@ -10224,12 +10219,12 @@
       <c r="E255">
         <v>10038</v>
       </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/euro-brokers</t>
+        </is>
+      </c>
       <c r="K255" t="inlineStr">
-        <is>
-          <t>https://voicescenter.org/living-memorial/memorials/euro-brokers</t>
-        </is>
-      </c>
-      <c r="L255" t="inlineStr">
         <is>
           <t>61 Employees</t>
         </is>
@@ -10254,7 +10249,7 @@
       <c r="E256">
         <v>10001</v>
       </c>
-      <c r="K256" t="inlineStr">
+      <c r="J256" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/fallen-friends-inwood</t>
         </is>
@@ -10279,12 +10274,12 @@
       <c r="E257">
         <v>11235</v>
       </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/fdny-lieutenant-dennis-mojica-way</t>
+        </is>
+      </c>
       <c r="K257" t="inlineStr">
-        <is>
-          <t>https://voicescenter.org/living-memorial/memorials/fdny-lieutenant-dennis-mojica-way</t>
-        </is>
-      </c>
-      <c r="L257" t="inlineStr">
         <is>
           <t>Dennis Mojica</t>
         </is>
@@ -10311,12 +10306,12 @@
       <c r="E258">
         <v>10006</v>
       </c>
-      <c r="K258" t="inlineStr">
+      <c r="J258" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/fdny-memorial-wall</t>
         </is>
       </c>
-      <c r="M258" t="inlineStr">
+      <c r="L258" t="inlineStr">
         <is>
           <t>http://www.fdnytenhouse.com/fdnywall/</t>
         </is>
@@ -10343,12 +10338,12 @@
       <c r="E259">
         <v>10306</v>
       </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/fire-patrolman-keith-roma-place</t>
+        </is>
+      </c>
       <c r="K259" t="inlineStr">
-        <is>
-          <t>https://voicescenter.org/living-memorial/memorials/fire-patrolman-keith-roma-place</t>
-        </is>
-      </c>
-      <c r="L259" t="inlineStr">
         <is>
           <t>Keith Roma</t>
         </is>
@@ -10375,12 +10370,12 @@
       <c r="E260">
         <v>11355</v>
       </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/firefighter-michael-j-cawley-place</t>
+        </is>
+      </c>
       <c r="K260" t="inlineStr">
-        <is>
-          <t>https://voicescenter.org/living-memorial/memorials/firefighter-michael-j-cawley-place</t>
-        </is>
-      </c>
-      <c r="L260" t="inlineStr">
         <is>
           <t>Michael J. Cawley</t>
         </is>
@@ -10405,12 +10400,12 @@
       <c r="E261">
         <v>11358</v>
       </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/firefighter-timothy-m-welty-street</t>
+        </is>
+      </c>
       <c r="K261" t="inlineStr">
-        <is>
-          <t>https://voicescenter.org/living-memorial/memorials/firefighter-timothy-m-welty-street</t>
-        </is>
-      </c>
-      <c r="L261" t="inlineStr">
         <is>
           <t>Firefighter Timothy M. Welty</t>
         </is>
@@ -10444,12 +10439,12 @@
       <c r="E262">
         <v>11221</v>
       </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/first-quincy-street-garden-memorial-nyc-black-firemen</t>
+        </is>
+      </c>
       <c r="K262" t="inlineStr">
-        <is>
-          <t>https://voicescenter.org/living-memorial/memorials/first-quincy-street-garden-memorial-nyc-black-firemen</t>
-        </is>
-      </c>
-      <c r="L262" t="inlineStr">
         <is>
           <t>The black firemen of NYC who perished in the September 11, 2001 World Trade Center disaster</t>
         </is>
@@ -10469,7 +10464,7 @@
       <c r="E263">
         <v>10458</v>
       </c>
-      <c r="K263" t="inlineStr">
+      <c r="J263" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/fordham-university-garden</t>
         </is>
@@ -10489,7 +10484,7 @@
       <c r="E264">
         <v>10458</v>
       </c>
-      <c r="K264" t="inlineStr">
+      <c r="J264" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/fordham-university-gym-seat</t>
         </is>
@@ -10509,7 +10504,7 @@
       <c r="E265">
         <v>11201</v>
       </c>
-      <c r="K265" t="inlineStr">
+      <c r="J265" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/fort-greene-park-groove-trees</t>
         </is>
@@ -10536,12 +10531,12 @@
       <c r="E266">
         <v>10314</v>
       </c>
-      <c r="K266" t="inlineStr">
+      <c r="J266" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/fresh-kills-memorial</t>
         </is>
       </c>
-      <c r="M266" t="inlineStr">
+      <c r="L266" t="inlineStr">
         <is>
           <t>http://www.sonicmemorial.org/public/freshkills/index.html</t>
         </is>
@@ -10572,12 +10567,12 @@
       <c r="E267">
         <v>10301</v>
       </c>
-      <c r="K267" t="inlineStr">
+      <c r="J267" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/garden-healing-staten-island-botanical-garden</t>
         </is>
       </c>
-      <c r="M267" t="inlineStr">
+      <c r="L267" t="inlineStr">
         <is>
           <t>http://www.visitstatenisland.com/attractions/snug-harbor-cultural-center-and-botanical-garden/</t>
         </is>
@@ -10602,17 +10597,17 @@
       <c r="E268">
         <v>10004</v>
       </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/gardens-remembrance-battery-park</t>
+        </is>
+      </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>https://voicescenter.org/living-memorial/memorials/gardens-remembrance-battery-park</t>
+          <t>Survivors</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
-        <is>
-          <t>Survivors</t>
-        </is>
-      </c>
-      <c r="M268" t="inlineStr">
         <is>
           <t>http://www.thebattery.org/gardens/</t>
         </is>
@@ -10632,7 +10627,7 @@
       <c r="E269">
         <v>10034</v>
       </c>
-      <c r="K269" t="inlineStr">
+      <c r="J269" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/good-shepherd-church-memorial-garden</t>
         </is>
@@ -10657,7 +10652,7 @@
       <c r="E270">
         <v>10002</v>
       </c>
-      <c r="K270" t="inlineStr">
+      <c r="J270" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/governor-garden</t>
         </is>
@@ -10682,7 +10677,7 @@
       <c r="E271">
         <v>11360</v>
       </c>
-      <c r="K271" t="inlineStr">
+      <c r="J271" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/greenstreet-triangle-bayside</t>
         </is>
@@ -10713,12 +10708,12 @@
       <c r="E272">
         <v>11220</v>
       </c>
-      <c r="K272" t="inlineStr">
+      <c r="J272" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/grove-healing-sunset-park</t>
         </is>
       </c>
-      <c r="M272" t="inlineStr">
+      <c r="L272" t="inlineStr">
         <is>
           <t>www.nyc.gov/parks</t>
         </is>
@@ -10749,12 +10744,12 @@
       <c r="E273">
         <v>10308</v>
       </c>
-      <c r="K273" t="inlineStr">
+      <c r="J273" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/grove-healing-seaside-nature-park</t>
         </is>
       </c>
-      <c r="M273" t="inlineStr">
+      <c r="L273" t="inlineStr">
         <is>
           <t>www.turnaroundfriends.org</t>
         </is>
@@ -10783,7 +10778,7 @@
       <c r="E274">
         <v>10454</v>
       </c>
-      <c r="K274" t="inlineStr">
+      <c r="J274" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/harmony-grove-peace-walk-and-labyrinth</t>
         </is>
@@ -10810,7 +10805,7 @@
       <c r="E275">
         <v>10304</v>
       </c>
-      <c r="K275" t="inlineStr">
+      <c r="J275" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/healing-garden-federated-garden-clubs-new-york-state</t>
         </is>
@@ -10835,7 +10830,7 @@
       <c r="E276">
         <v>11694</v>
       </c>
-      <c r="K276" t="inlineStr">
+      <c r="J276" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/heavens-over-rockaway</t>
         </is>
@@ -10866,12 +10861,12 @@
       <c r="E277">
         <v>10033</v>
       </c>
-      <c r="K277" t="inlineStr">
+      <c r="J277" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/highbridge-park-living-memorial</t>
         </is>
       </c>
-      <c r="M277" t="inlineStr">
+      <c r="L277" t="inlineStr">
         <is>
           <t>www.nyrp.org</t>
         </is>
@@ -10891,17 +10886,17 @@
       <c r="E278">
         <v>10312</v>
       </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/holy-child-911-memorial-playground</t>
+        </is>
+      </c>
       <c r="K278" t="inlineStr">
         <is>
-          <t>https://voicescenter.org/living-memorial/memorials/holy-child-911-memorial-playground</t>
+          <t>Joseph Ianelli &amp; Don DeFranco</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
-        <is>
-          <t>Joseph Ianelli &amp; Don DeFranco</t>
-        </is>
-      </c>
-      <c r="M278" t="inlineStr">
         <is>
           <t>www.josephianelli.org</t>
         </is>
@@ -10921,12 +10916,12 @@
       <c r="E279">
         <v>10312</v>
       </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/huguenot-park-library-911-memorial</t>
+        </is>
+      </c>
       <c r="K279" t="inlineStr">
-        <is>
-          <t>https://voicescenter.org/living-memorial/memorials/huguenot-park-library-911-memorial</t>
-        </is>
-      </c>
-      <c r="L279" t="inlineStr">
         <is>
           <t>Michael Cammarata</t>
         </is>
@@ -10946,7 +10941,7 @@
       <c r="E280">
         <v>10019</v>
       </c>
-      <c r="K280" t="inlineStr">
+      <c r="J280" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/john-dallara-and-rodney-gillis-library</t>
         </is>
@@ -10966,7 +10961,7 @@
       <c r="E281">
         <v>10312</v>
       </c>
-      <c r="K281" t="inlineStr">
+      <c r="J281" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/joseph-ianelli-don-defranco-holy-child-911-memorial-playground</t>
         </is>
@@ -10991,7 +10986,7 @@
       <c r="E282">
         <v>11362</v>
       </c>
-      <c r="K282" t="inlineStr">
+      <c r="J282" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/junior-high-school-67-louis-pasteur</t>
         </is>
@@ -11016,12 +11011,12 @@
       <c r="E283">
         <v>10065</v>
       </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/keefe-bruyette-woods-911-memorial-plaque</t>
+        </is>
+      </c>
       <c r="K283" t="inlineStr">
-        <is>
-          <t>https://voicescenter.org/living-memorial/memorials/keefe-bruyette-woods-911-memorial-plaque</t>
-        </is>
-      </c>
-      <c r="L283" t="inlineStr">
         <is>
           <t>67 KBW Colleagues who lost their lives on 9/11</t>
         </is>
@@ -11041,7 +11036,7 @@
       <c r="E284">
         <v>11201</v>
       </c>
-      <c r="K284" t="inlineStr">
+      <c r="J284" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/ladder-118-engine-205</t>
         </is>
@@ -11061,7 +11056,7 @@
       <c r="E285">
         <v>10468</v>
       </c>
-      <c r="K285" t="inlineStr">
+      <c r="J285" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/lehman-college-memorial</t>
         </is>
@@ -11088,12 +11083,12 @@
       <c r="E286">
         <v>11225</v>
       </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/liberty-oaks-911-memorial</t>
+        </is>
+      </c>
       <c r="K286" t="inlineStr">
-        <is>
-          <t>https://voicescenter.org/living-memorial/memorials/liberty-oaks-911-memorial</t>
-        </is>
-      </c>
-      <c r="L286" t="inlineStr">
         <is>
           <t>The remembrance of the events of September 11, 2001 and those who lost their lives on that day.</t>
         </is>
@@ -11118,12 +11113,12 @@
       <c r="E287">
         <v>11230</v>
       </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/liberty-oaks-911-memorial-0</t>
+        </is>
+      </c>
       <c r="K287" t="inlineStr">
-        <is>
-          <t>https://voicescenter.org/living-memorial/memorials/liberty-oaks-911-memorial-0</t>
-        </is>
-      </c>
-      <c r="L287" t="inlineStr">
         <is>
           <t>All of those who lost their lives</t>
         </is>
@@ -11150,12 +11145,12 @@
       <c r="E288">
         <v>10013</v>
       </c>
-      <c r="K288" t="inlineStr">
+      <c r="J288" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/living-memorial-grove</t>
         </is>
       </c>
-      <c r="M288" t="inlineStr">
+      <c r="L288" t="inlineStr">
         <is>
           <t>http://www.livingmemorialsproject.net</t>
         </is>
@@ -11183,12 +11178,12 @@
       <c r="E289">
         <v>10473</v>
       </c>
-      <c r="K289" t="inlineStr">
+      <c r="J289" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/living-memorial-trail</t>
         </is>
       </c>
-      <c r="M289" t="inlineStr">
+      <c r="L289" t="inlineStr">
         <is>
           <t>https://www.ssbx.org</t>
         </is>
@@ -11213,12 +11208,12 @@
       <c r="E290">
         <v>10001</v>
       </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/mark-and-stephen-colaio-way</t>
+        </is>
+      </c>
       <c r="K290" t="inlineStr">
-        <is>
-          <t>https://voicescenter.org/living-memorial/memorials/mark-and-stephen-colaio-way</t>
-        </is>
-      </c>
-      <c r="L290" t="inlineStr">
         <is>
           <t>Mark and Stephen Colaio</t>
         </is>
@@ -11243,7 +11238,7 @@
       <c r="E291">
         <v>10128</v>
       </c>
-      <c r="K291" t="inlineStr">
+      <c r="J291" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/mark-jardim-bench-central-park</t>
         </is>
@@ -11271,17 +11266,17 @@
       <c r="E292">
         <v>10036</v>
       </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/marsh-mclennan-september-11th-memorial</t>
+        </is>
+      </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t>https://voicescenter.org/living-memorial/memorials/marsh-mclennan-september-11th-memorial</t>
+          <t>The memorial serves to honor the 295 members of the MMC family and 63 consultants that were lost on September 11th</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
-        <is>
-          <t>The memorial serves to honor the 295 members of the MMC family and 63 consultants that were lost on September 11th</t>
-        </is>
-      </c>
-      <c r="M292" t="inlineStr">
         <is>
           <t>http://memorial.mmc.com/</t>
         </is>
@@ -11308,7 +11303,7 @@
       <c r="E293">
         <v>11378</v>
       </c>
-      <c r="K293" t="inlineStr">
+      <c r="J293" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/maspeth-queens-we-remember</t>
         </is>
@@ -11333,7 +11328,7 @@
       <c r="E294">
         <v>10306</v>
       </c>
-      <c r="K294" t="inlineStr">
+      <c r="J294" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/matthew-j-grzymalski-drive</t>
         </is>
@@ -11360,12 +11355,12 @@
       <c r="E295">
         <v>11377</v>
       </c>
-      <c r="K295" t="inlineStr">
+      <c r="J295" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/memorial-treeway-champion-trees-calvary-cemetary</t>
         </is>
       </c>
-      <c r="M295" t="inlineStr">
+      <c r="L295" t="inlineStr">
         <is>
           <t>www.championtreeproject.org</t>
         </is>
@@ -11390,12 +11385,12 @@
       <c r="E296">
         <v>11385</v>
       </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/michael-marti-street</t>
+        </is>
+      </c>
       <c r="K296" t="inlineStr">
-        <is>
-          <t>https://voicescenter.org/living-memorial/memorials/michael-marti-street</t>
-        </is>
-      </c>
-      <c r="L296" t="inlineStr">
         <is>
           <t>Michael A. Marti</t>
         </is>
@@ -11420,12 +11415,12 @@
       <c r="E297">
         <v>10024</v>
       </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/michael-armstrong-bench</t>
+        </is>
+      </c>
       <c r="K297" t="inlineStr">
-        <is>
-          <t>https://voicescenter.org/living-memorial/memorials/michael-armstrong-bench</t>
-        </is>
-      </c>
-      <c r="L297" t="inlineStr">
         <is>
           <t>Michael J. Armstrong</t>
         </is>
@@ -11450,12 +11445,12 @@
       <c r="E298">
         <v>10022</v>
       </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/michael-hardy-edwards-tree</t>
+        </is>
+      </c>
       <c r="K298" t="inlineStr">
-        <is>
-          <t>https://voicescenter.org/living-memorial/memorials/michael-hardy-edwards-tree</t>
-        </is>
-      </c>
-      <c r="L298" t="inlineStr">
         <is>
           <t>Michael Hardy Edwards.</t>
         </is>
@@ -11475,7 +11470,7 @@
       <c r="E299">
         <v>10003</v>
       </c>
-      <c r="K299" t="inlineStr">
+      <c r="J299" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/mj-armstrongs-public-house</t>
         </is>
@@ -11495,7 +11490,7 @@
       <c r="E300">
         <v>10306</v>
       </c>
-      <c r="K300" t="inlineStr">
+      <c r="J300" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/monsignor-farrell-hs-wall-remembrance</t>
         </is>
@@ -11526,17 +11521,17 @@
       <c r="E301">
         <v>10006</v>
       </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/national-september-11-memorial-museum</t>
+        </is>
+      </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t>https://voicescenter.org/living-memorial/memorials/national-september-11-memorial-museum</t>
+          <t>The nearly 3,000 people killed in the terror attacks of September 11, 2001 at the World Trade Center site, near Shanksville, Pa., and at the Pentagon, as well as the six people killed in the World Trade Center bombing in February 1993.</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
-        <is>
-          <t>The nearly 3,000 people killed in the terror attacks of September 11, 2001 at the World Trade Center site, near Shanksville, Pa., and at the Pentagon, as well as the six people killed in the World Trade Center bombing in February 1993.</t>
-        </is>
-      </c>
-      <c r="M301" t="inlineStr">
         <is>
           <t>http://www.911memorial.org</t>
         </is>
@@ -11561,7 +11556,7 @@
       <c r="E302">
         <v>10038</v>
       </c>
-      <c r="K302" t="inlineStr">
+      <c r="J302" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/new-york-city-police-memorial-wall</t>
         </is>
@@ -11586,7 +11581,7 @@
       <c r="E303">
         <v>10012</v>
       </c>
-      <c r="K303" t="inlineStr">
+      <c r="J303" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/new-york-university-stern-school-business</t>
         </is>
@@ -11606,7 +11601,7 @@
       <c r="E304">
         <v>10001</v>
       </c>
-      <c r="K304" t="inlineStr">
+      <c r="J304" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/nyu-shimkin-lobby</t>
         </is>
@@ -11626,7 +11621,7 @@
       <c r="E305">
         <v>11209</v>
       </c>
-      <c r="K305" t="inlineStr">
+      <c r="J305" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/our-lady-angels</t>
         </is>
@@ -11653,7 +11648,7 @@
       <c r="E306">
         <v>11230</v>
       </c>
-      <c r="K306" t="inlineStr">
+      <c r="J306" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/paul-salvio-memorial-softball-game</t>
         </is>
@@ -11673,7 +11668,7 @@
       <c r="E307">
         <v>10301</v>
       </c>
-      <c r="K307" t="inlineStr">
+      <c r="J307" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/petrides-school-athletic-field</t>
         </is>
@@ -11698,7 +11693,7 @@
       <c r="E308">
         <v>11209</v>
       </c>
-      <c r="K308" t="inlineStr">
+      <c r="J308" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/poly-prep-memorial-911-garden-remembrance</t>
         </is>
@@ -11723,7 +11718,7 @@
       <c r="E309">
         <v>10302</v>
       </c>
-      <c r="K309" t="inlineStr">
+      <c r="J309" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/postcards-memorial</t>
         </is>
@@ -11749,7 +11744,7 @@
       <c r="E310">
         <v>11207</v>
       </c>
-      <c r="K310" t="inlineStr">
+      <c r="J310" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/ps4k-paradise-garden</t>
         </is>
@@ -11769,12 +11764,12 @@
       <c r="E311">
         <v>10005</v>
       </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/queen-elizabeth-ii-september-11-memorial-garden</t>
+        </is>
+      </c>
       <c r="K311" t="inlineStr">
-        <is>
-          <t>https://voicescenter.org/living-memorial/memorials/queen-elizabeth-ii-september-11-memorial-garden</t>
-        </is>
-      </c>
-      <c r="L311" t="inlineStr">
         <is>
           <t>The memorial garden represents not just the 67 British victims of 9/11, but also those from all 54 Commonwealth countries, including Australia and Canada.</t>
         </is>
@@ -11814,12 +11809,12 @@
       <c r="E312">
         <v>11370</v>
       </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/queens-firefighter-memorial</t>
+        </is>
+      </c>
       <c r="K312" t="inlineStr">
-        <is>
-          <t>https://voicescenter.org/living-memorial/memorials/queens-firefighter-memorial</t>
-        </is>
-      </c>
-      <c r="L312" t="inlineStr">
         <is>
           <t>The 76 Queens Firefighters killed on September 11th</t>
         </is>
@@ -11839,12 +11834,12 @@
       <c r="E313">
         <v>11414</v>
       </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/richard-pearlman-memorial-garden</t>
+        </is>
+      </c>
       <c r="K313" t="inlineStr">
-        <is>
-          <t>https://voicescenter.org/living-memorial/memorials/richard-pearlman-memorial-garden</t>
-        </is>
-      </c>
-      <c r="L313" t="inlineStr">
         <is>
           <t>Richard Pearlman</t>
         </is>
@@ -11871,12 +11866,12 @@
       <c r="E314">
         <v>11355</v>
       </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/richard-pearlman-memorial-tree</t>
+        </is>
+      </c>
       <c r="K314" t="inlineStr">
-        <is>
-          <t>https://voicescenter.org/living-memorial/memorials/richard-pearlman-memorial-tree</t>
-        </is>
-      </c>
-      <c r="L314" t="inlineStr">
         <is>
           <t>Richard Pearlman</t>
         </is>
@@ -11901,17 +11896,17 @@
       <c r="E315">
         <v>11694</v>
       </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/rockaway-partnership-waterfront-tribute-park</t>
+        </is>
+      </c>
       <c r="K315" t="inlineStr">
         <is>
-          <t>https://voicescenter.org/living-memorial/memorials/rockaway-partnership-waterfront-tribute-park</t>
+          <t>Those who lost their lives in the terrorist attacks of 9/11, both in the community and in total.</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
-        <is>
-          <t>Those who lost their lives in the terrorist attacks of 9/11, both in the community and in total.</t>
-        </is>
-      </c>
-      <c r="M315" t="inlineStr">
         <is>
           <t>https://www.rockawaychamberofcommerce.com</t>
         </is>
@@ -11931,7 +11926,7 @@
       <c r="E316">
         <v>10044</v>
       </c>
-      <c r="K316" t="inlineStr">
+      <c r="J316" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/roosevelt-island-911-memorial</t>
         </is>
@@ -11958,12 +11953,12 @@
       <c r="E317">
         <v>10305</v>
       </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/sacred-heart-statue-church-holy-rosary</t>
+        </is>
+      </c>
       <c r="K317" t="inlineStr">
-        <is>
-          <t>https://voicescenter.org/living-memorial/memorials/sacred-heart-statue-church-holy-rosary</t>
-        </is>
-      </c>
-      <c r="L317" t="inlineStr">
         <is>
           <t>Laura Angilletta</t>
         </is>
@@ -11988,12 +11983,12 @@
       <c r="E318">
         <v>10304</v>
       </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/sandra-conaty-brace-way</t>
+        </is>
+      </c>
       <c r="K318" t="inlineStr">
-        <is>
-          <t>https://voicescenter.org/living-memorial/memorials/sandra-conaty-brace-way</t>
-        </is>
-      </c>
-      <c r="L318" t="inlineStr">
         <is>
           <t>Sandra Brace</t>
         </is>
@@ -12018,12 +12013,12 @@
       <c r="E319">
         <v>8820</v>
       </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/scott-schertzer-memorial-bench</t>
+        </is>
+      </c>
       <c r="K319" t="inlineStr">
-        <is>
-          <t>https://voicescenter.org/living-memorial/memorials/scott-schertzer-memorial-bench</t>
-        </is>
-      </c>
-      <c r="L319" t="inlineStr">
         <is>
           <t>Scott Schertzer</t>
         </is>
@@ -12052,7 +12047,7 @@
       <c r="E320">
         <v>11220</v>
       </c>
-      <c r="K320" t="inlineStr">
+      <c r="J320" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/september-11-beacon-memorial-pier-69</t>
         </is>
@@ -12079,17 +12074,17 @@
       <c r="E321">
         <v>11235</v>
       </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/september-11-family-group-russian-family-memorial</t>
+        </is>
+      </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t>https://voicescenter.org/living-memorial/memorials/september-11-family-group-russian-family-memorial</t>
+          <t>Honor New Yorkers of Russian descent who lost their lives in the World Trade Center on September 11, 2001.</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
-        <is>
-          <t>Honor New Yorkers of Russian descent who lost their lives in the World Trade Center on September 11, 2001.</t>
-        </is>
-      </c>
-      <c r="M321" t="inlineStr">
         <is>
           <t>http://www.september11familygroup.org</t>
         </is>
@@ -12116,17 +12111,17 @@
       <c r="E322">
         <v>11225</v>
       </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/september-11-memorial-grove-prospect-park</t>
+        </is>
+      </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t>https://voicescenter.org/living-memorial/memorials/september-11-memorial-grove-prospect-park</t>
+          <t>The lives of people from Brooklyn that were lost on Sept. 11th</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
-        <is>
-          <t>The lives of people from Brooklyn that were lost on Sept. 11th</t>
-        </is>
-      </c>
-      <c r="M322" t="inlineStr">
         <is>
           <t>http://www.prospectpark.org</t>
         </is>
@@ -12151,12 +12146,12 @@
       <c r="E323">
         <v>11224</v>
       </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/september-11-memorial-square</t>
+        </is>
+      </c>
       <c r="K323" t="inlineStr">
-        <is>
-          <t>https://voicescenter.org/living-memorial/memorials/september-11-memorial-square</t>
-        </is>
-      </c>
-      <c r="L323" t="inlineStr">
         <is>
           <t>The victims of the WTC tragedy and among them New Yorkers of Russian descent who lost their lives on that tragic day.</t>
         </is>
@@ -12183,17 +12178,17 @@
       <c r="E324">
         <v>11228</v>
       </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/september-11th-garden-hope</t>
+        </is>
+      </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t>https://voicescenter.org/living-memorial/memorials/september-11th-garden-hope</t>
+          <t>The 9 members of St. Ephrem's Church who were lost on September 11th.</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
-        <is>
-          <t>The 9 members of St. Ephrem's Church who were lost on September 11th.</t>
-        </is>
-      </c>
-      <c r="M324" t="inlineStr">
         <is>
           <t>http://www.homereporternews.com/news/general/article_b80e6c54-db38-11e0-b8c4-001cc4c002e0.html</t>
         </is>
@@ -12221,17 +12216,17 @@
       <c r="E325">
         <v>11421</v>
       </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/september-11th-community-memorial-garden-forest-park</t>
+        </is>
+      </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t>https://voicescenter.org/living-memorial/memorials/september-11th-community-memorial-garden-forest-park</t>
+          <t>The members of the Forest Park community who died on 9-11, as well as the uniformed personnel from Queens who perished.</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
-        <is>
-          <t>The members of the Forest Park community who died on 9-11, as well as the uniformed personnel from Queens who perished.</t>
-        </is>
-      </c>
-      <c r="M325" t="inlineStr">
         <is>
           <t>www.nyforestpark.net</t>
         </is>
@@ -12256,12 +12251,12 @@
       <c r="E326">
         <v>10022</v>
       </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/smith-wollenskys-grill</t>
+        </is>
+      </c>
       <c r="K326" t="inlineStr">
-        <is>
-          <t>https://voicescenter.org/living-memorial/memorials/smith-wollenskys-grill</t>
-        </is>
-      </c>
-      <c r="L326" t="inlineStr">
         <is>
           <t>Robert Andrew Spencer and Andrew H. Golkin</t>
         </is>
@@ -12288,17 +12283,17 @@
       <c r="E327">
         <v>10301</v>
       </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/snug-harbor-cultural-center-and-botanical-garden-tribute-center</t>
+        </is>
+      </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t>https://voicescenter.org/living-memorial/memorials/snug-harbor-cultural-center-and-botanical-garden-tribute-center</t>
+          <t>In tribute to the men and women lost in the tragic attack on New York City on September 11, 2001</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
-        <is>
-          <t>In tribute to the men and women lost in the tragic attack on New York City on September 11, 2001</t>
-        </is>
-      </c>
-      <c r="M327" t="inlineStr">
         <is>
           <t>http://snug-harbor.org/</t>
         </is>
@@ -12323,12 +12318,12 @@
       <c r="E328">
         <v>10314</v>
       </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/spirit-911</t>
+        </is>
+      </c>
       <c r="K328" t="inlineStr">
-        <is>
-          <t>https://voicescenter.org/living-memorial/memorials/spirit-911</t>
-        </is>
-      </c>
-      <c r="L328" t="inlineStr">
         <is>
           <t>Staten Island victims of 9/11.</t>
         </is>
@@ -12353,7 +12348,7 @@
       <c r="E329">
         <v>11362</v>
       </c>
-      <c r="K329" t="inlineStr">
+      <c r="J329" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/st-anastasia-roman-catholic-church-stained-glass-window</t>
         </is>
@@ -12378,7 +12373,7 @@
       <c r="E330">
         <v>10306</v>
       </c>
-      <c r="K330" t="inlineStr">
+      <c r="J330" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/st-patrick-statue-st-margaret-mary-church</t>
         </is>
@@ -12405,17 +12400,17 @@
       <c r="E331">
         <v>10301</v>
       </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/staten-island-911-postcards-memorial</t>
+        </is>
+      </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t>https://voicescenter.org/living-memorial/memorials/staten-island-911-postcards-memorial</t>
+          <t>The 274 victims of Staten Island killed on 9/11</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
-        <is>
-          <t>The 274 victims of Staten Island killed on 9/11</t>
-        </is>
-      </c>
-      <c r="M331" t="inlineStr">
         <is>
           <t>http://www.yelp.com/biz/staten-island-september-11-memorial-staten-island</t>
         </is>
@@ -12435,7 +12430,7 @@
       <c r="E332">
         <v>10306</v>
       </c>
-      <c r="K332" t="inlineStr">
+      <c r="J332" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/statue-st-patrick</t>
         </is>
@@ -12462,12 +12457,12 @@
       <c r="E333">
         <v>10048</v>
       </c>
-      <c r="K333" t="inlineStr">
+      <c r="J333" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/suntowers</t>
         </is>
       </c>
-      <c r="M333" t="inlineStr">
+      <c r="L333" t="inlineStr">
         <is>
           <t>www.redseeds.com</t>
         </is>
@@ -12492,12 +12487,12 @@
       <c r="E334">
         <v>10301</v>
       </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/jason-defazio-memorial</t>
+        </is>
+      </c>
       <c r="K334" t="inlineStr">
-        <is>
-          <t>https://voicescenter.org/living-memorial/memorials/jason-defazio-memorial</t>
-        </is>
-      </c>
-      <c r="L334" t="inlineStr">
         <is>
           <t>Jason DeFazio</t>
         </is>
@@ -12522,7 +12517,7 @@
       <c r="E335">
         <v>11362</v>
       </c>
-      <c r="K335" t="inlineStr">
+      <c r="J335" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/thornville-avenue-marathon-parkway-street-naming</t>
         </is>
@@ -12549,12 +12544,12 @@
       <c r="E336">
         <v>10460</v>
       </c>
-      <c r="K336" t="inlineStr">
+      <c r="J336" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/trees-life-and-unity-bronx</t>
         </is>
       </c>
-      <c r="M336" t="inlineStr">
+      <c r="L336" t="inlineStr">
         <is>
           <t>www.greenguerillas.org</t>
         </is>
@@ -12582,12 +12577,12 @@
       <c r="E337">
         <v>11221</v>
       </c>
-      <c r="K337" t="inlineStr">
+      <c r="J337" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/trees-life-and-unity-brooklyn</t>
         </is>
       </c>
-      <c r="M337" t="inlineStr">
+      <c r="L337" t="inlineStr">
         <is>
           <t>www.greenguerillas.org</t>
         </is>
@@ -12607,7 +12602,7 @@
       <c r="E338">
         <v>11354</v>
       </c>
-      <c r="K338" t="inlineStr">
+      <c r="J338" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/vincent-cangelosi-memorial-way</t>
         </is>
@@ -12632,12 +12627,12 @@
       <c r="E339">
         <v>10024</v>
       </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/vincent-m-boland-jr-bench</t>
+        </is>
+      </c>
       <c r="K339" t="inlineStr">
-        <is>
-          <t>https://voicescenter.org/living-memorial/memorials/vincent-m-boland-jr-bench</t>
-        </is>
-      </c>
-      <c r="L339" t="inlineStr">
         <is>
           <t>Vincent M. Boland, Jr.</t>
         </is>
@@ -12662,7 +12657,7 @@
       <c r="E340">
         <v>11232</v>
       </c>
-      <c r="K340" t="inlineStr">
+      <c r="J340" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/vladimir-savinkin-memorial-bench-0</t>
         </is>
@@ -12687,12 +12682,12 @@
       <c r="E341">
         <v>10310</v>
       </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/walker-park-911-memorial-tennis-courts</t>
+        </is>
+      </c>
       <c r="K341" t="inlineStr">
-        <is>
-          <t>https://voicescenter.org/living-memorial/memorials/walker-park-911-memorial-tennis-courts</t>
-        </is>
-      </c>
-      <c r="L341" t="inlineStr">
         <is>
           <t>Charles L. Kasper</t>
         </is>
@@ -12717,7 +12712,7 @@
       <c r="E342">
         <v>11224</v>
       </c>
-      <c r="K342" t="inlineStr">
+      <c r="J342" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/wall-remembrance</t>
         </is>
@@ -12737,7 +12732,7 @@
       <c r="E343">
         <v>10306</v>
       </c>
-      <c r="K343" t="inlineStr">
+      <c r="J343" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/we-remember-911-farrell-high-school</t>
         </is>
@@ -12762,12 +12757,12 @@
       <c r="E344">
         <v>10025</v>
       </c>
-      <c r="K344" t="inlineStr">
+      <c r="J344" t="inlineStr">
         <is>
           <t>https://voicescenter.org/living-memorial/memorials/west-104th-st-garden</t>
         </is>
       </c>
-      <c r="M344" t="inlineStr">
+      <c r="L344" t="inlineStr">
         <is>
           <t>http://www.west104garden.org/</t>
         </is>
@@ -12792,12 +12787,12 @@
       <c r="E345">
         <v>10024</v>
       </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/william-bill-godshalk-memorial-bench</t>
+        </is>
+      </c>
       <c r="K345" t="inlineStr">
-        <is>
-          <t>https://voicescenter.org/living-memorial/memorials/william-bill-godshalk-memorial-bench</t>
-        </is>
-      </c>
-      <c r="L345" t="inlineStr">
         <is>
           <t>William Robert Godshalk</t>
         </is>
@@ -12844,12 +12839,12 @@
       <c r="E346">
         <v>11228</v>
       </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>https://voicescenter.org/living-memorial/memorials/xaverian-high-school-911-memorial</t>
+        </is>
+      </c>
       <c r="K346" t="inlineStr">
-        <is>
-          <t>https://voicescenter.org/living-memorial/memorials/xaverian-high-school-911-memorial</t>
-        </is>
-      </c>
-      <c r="L346" t="inlineStr">
         <is>
           <t>The 23 Lost Alumni from Xaverian High School</t>
         </is>
